--- a/tame_output/ON/bt/strategyON_20230801.xlsx
+++ b/tame_output/ON/bt/strategyON_20230801.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.9%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>104.4%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.0%</t>
+          <t>141.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1675"/>
+  <dimension ref="A1:G1676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40035,7 +40035,7 @@
         <v>45137</v>
       </c>
       <c r="B1675" t="n">
-        <v>2.885843256651356</v>
+        <v>2.885368413286558</v>
       </c>
       <c r="C1675" t="n">
         <v>3.005015340003198</v>
@@ -40051,6 +40051,29 @@
       </c>
       <c r="G1675" t="n">
         <v>4.282973550111265</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="2" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B1676" t="n">
+        <v>2.867762540130417</v>
+      </c>
+      <c r="C1676" t="n">
+        <v>3.003825991470496</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>1.531546381132771</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>3.616088119609857</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>2.146025346711119</v>
+      </c>
+      <c r="G1676" t="n">
+        <v>4.291441199497169</v>
       </c>
     </row>
   </sheetData>
